--- a/artfynd/A 33512-2025 artfynd.xlsx
+++ b/artfynd/A 33512-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126334373</v>
       </c>
       <c r="B2" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>126331631</v>
       </c>
       <c r="B3" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
